--- a/starter-kit/data/phieu-sua-thang-6.xlsx
+++ b/starter-kit/data/phieu-sua-thang-6.xlsx
@@ -31,8 +31,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>ma_ps</t>
   </si>
@@ -62,9 +84,6 @@
   </si>
   <si>
     <t>SM03</t>
-  </si>
-  <si>
-    <t>=VLOOKUP(C2,BangGiaSua!$A2:$A8,False(BangGiaSua!B2:B8))</t>
   </si>
   <si>
     <t>PS002</t>
@@ -200,14 +219,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -663,154 +675,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1199,19 +1210,20 @@
       <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
+      <c r="E2" t="e" cm="1">
+        <f t="array" ref="E2">VLOOKUP(C2,BangGiaSua!$A2:$A8,BangGiaSua!B2:B8)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -1219,10 +1231,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -1233,13 +1245,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1247,13 +1259,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1261,13 +1273,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1275,13 +1287,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -1289,13 +1301,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -1303,13 +1315,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -1317,10 +1329,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
         <v>32</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -1331,13 +1343,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1345,13 +1357,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1359,13 +1371,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1373,13 +1385,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -1387,13 +1399,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1430,10 +1442,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>150000</v>
@@ -1441,10 +1453,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>200000</v>
@@ -1455,7 +1467,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4">
         <v>250000</v>
@@ -1463,10 +1475,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <v>350000</v>
@@ -1474,10 +1486,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>600000</v>
@@ -1485,10 +1497,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>400000</v>
@@ -1496,10 +1508,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8">
         <v>800000</v>
